--- a/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ORCHESTRATION WITH APACHE AIRFLOW/Apache Airflow Introduction/apache_airflow_intro_questions.xlsx
+++ b/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ORCHESTRATION WITH APACHE AIRFLOW/Apache Airflow Introduction/apache_airflow_intro_questions.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apache Airflow Intro" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
+          <t>Explanation</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Explanation</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -454,15 +454,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Airflow was created at Airbnb in 2014.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Airflow was created at Airbnb in 2014.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -477,15 +476,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>Airflow graduated to Top-Level Project in January 2019.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Airflow graduated to Top-Level Project in January 2019.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -500,15 +498,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Airflow is written in Python and workflows are defined in Python.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Airflow is written in Python and workflows are defined in Python.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -530,12 +527,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Airflow is designed for orchestrating and scheduling data workflows.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Airflow is designed for orchestrating and scheduling data workflows.</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -550,15 +547,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DAG</t>
+          <t>A DAG (Directed Acyclic Graph) defines the entire workflow.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>A DAG (Directed Acyclic Graph) defines the entire workflow.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -573,15 +569,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Airbnb developed Airflow to manage their complex data workflows.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Airbnb developed Airflow to manage their complex data workflows.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -603,12 +598,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Airflow allows defining workflows in Python which is ideal for Python-based scripts.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Airflow allows defining workflows in Python which is ideal for Python-based scripts.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -623,15 +618,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>pip install apache-airflow</t>
+          <t>Use pip to install Airflow.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Use pip to install Airflow.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -646,15 +640,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Workflow engine</t>
+          <t>Airflow orchestrates tasks but doesn't process data itself.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Airflow orchestrates tasks but doesn't process data itself.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -669,15 +662,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Operators</t>
+          <t>Operators define individual tasks and their dependencies.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Operators define individual tasks and their dependencies.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -692,15 +684,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Webserver</t>
+          <t>The webserver provides the UI for monitoring and managing workflows.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The webserver provides the UI for monitoring and managing workflows.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -715,15 +706,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Airflow uses a metadata database like PostgreSQL or MySQL.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Airflow uses a metadata database like PostgreSQL or MySQL.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -745,12 +735,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Airflow supports distributed execution with multiple workers.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Airflow supports distributed execution with multiple workers.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -765,15 +755,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Scheduling</t>
+          <t>The scheduler triggers workflows based on defined schedules.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The scheduler triggers workflows based on defined schedules.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -788,15 +777,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>A task is a single unit of work in an Airflow DAG.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>A task is a single unit of work in an Airflow DAG.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -811,15 +799,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>Airflow DAGs are defined in Python files.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Airflow DAGs are defined in Python files.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -834,15 +821,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.7+</t>
+          <t>Airflow 2.0+ requires Python 3.7 or higher.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Airflow 2.0+ requires Python 3.7 or higher.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -864,12 +850,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Airflow has built-in retry mechanisms for failed tasks.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Airflow has built-in retry mechanisms for failed tasks.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -884,15 +870,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>airflow</t>
+          <t>The CLI is accessed using the 'airflow' command.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>The CLI is accessed using the 'airflow' command.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -907,15 +892,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Celery workers</t>
+          <t>Flower monitors Celery workers when using CeleryExecutor.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Flower monitors Celery workers when using CeleryExecutor.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
